--- a/data_cleaning_template.xlsx
+++ b/data_cleaning_template.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Liu\Devel-Git\UnitTests\Sql\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78772CC7-62C4-44A8-BA2B-D1A6AE60E0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="ConfigTable" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,22 +38,22 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{3C637903-E06C-4458-8ACC-5D57BCE12BA0}" name="Query - GetCleanData" description="Connection to the 'GetCleanData' query in the workbook." type="100" refreshedVersion="8" minRefreshableVersion="5">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="Query - GetCleanData" description="Connection to the 'GetCleanData' query in the workbook." type="100" refreshedVersion="8" minRefreshableVersion="5">
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="a51b5d6f-4996-48af-a06d-3cde9c5596cb"/>
       </ext>
     </extLst>
   </connection>
-  <connection id="2" xr16:uid="{929FA5DC-AB66-4C13-88EA-712A8A8446D6}" name="Query - GetCleaningLog" description="Connection to the 'GetCleaningLog' query in the workbook." type="100" refreshedVersion="8" minRefreshableVersion="5" saveData="1">
+  <connection id="2" name="Query - GetCleaningLog" description="Connection to the 'GetCleaningLog' query in the workbook." type="100" refreshedVersion="8" minRefreshableVersion="5" saveData="1">
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="3645d3ae-63a0-4041-b2d7-31c60e8b1640"/>
       </ext>
     </extLst>
   </connection>
-  <connection id="3" xr16:uid="{BA2348F7-346E-4759-B901-A94397DA930F}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
+  <connection id="3" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
     <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
     <extLst>
@@ -69,28 +63,6 @@
     </extLst>
   </connection>
 </connections>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -108,7 +80,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -166,7 +138,6 @@
         <sz val="11"/>
         <color rgb="FF0F1115"/>
         <name val="Segoe UI"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -184,13 +155,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{729B0DB4-5D23-452D-9644-899E90E13094}" name="ConfigTable" displayName="ConfigTable" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2" xr:uid="{729B0DB4-5D23-452D-9644-899E90E13094}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ConfigTable" displayName="ConfigTable" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{89FB25FD-B696-44CF-B2D8-6F1B27446CF1}" name="Parameter" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{9C23E68E-9CFD-4B4D-8CFD-AEE4F34E7BAB}" name="Value">
-      <calculatedColumnFormula array="1">LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" name="Parameter" dataDxfId="0"/>
+    <tableColumn id="2" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -239,7 +208,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -274,7 +243,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -451,14 +420,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -478,10 +447,6 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="str" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">LEFT(CELL("filename",A1),FIND("[",CELL("filename",A1))-1)</f>
-        <v>D:\Liu\Devel-Git\UnitTests\Sql\</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
